--- a/1913.HK.xlsx
+++ b/1913.HK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79E34AFD-B232-477F-857F-B3469690F6A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF397BB-7378-46E0-B6A7-5ABEED101AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="3" xr2:uid="{139B0E69-D4C6-42BA-824B-D7880A74E282}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{139B0E69-D4C6-42BA-824B-D7880A74E282}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="392">
   <si>
     <t xml:space="preserve">Prada </t>
   </si>
@@ -1255,6 +1255,27 @@
   <si>
     <t>n.a.</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>MiuMiu Growth</t>
+  </si>
+  <si>
+    <t>Versace Growth</t>
+  </si>
+  <si>
+    <t>Chuchs Growth</t>
+  </si>
 </sst>
 </file>
 
@@ -1271,13 +1292,19 @@
     <numFmt numFmtId="171" formatCode="&quot;FY&quot;0&quot;A&quot;"/>
     <numFmt numFmtId="172" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1622,167 +1649,171 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="8" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="9" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="18" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2233,7 +2264,7 @@
         <v>120</v>
       </c>
       <c r="H2" s="2">
-        <v>40.880000000000003</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -2268,7 +2299,7 @@
       </c>
       <c r="H3" s="2">
         <f>+H2*H10</f>
-        <v>4.9055999999999997</v>
+        <v>4.1640000000000006</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -2343,7 +2374,7 @@
       </c>
       <c r="H5" s="8">
         <f>+H3*H4</f>
-        <v>12552.5670144</v>
+        <v>10654.943136000002</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -2459,7 +2490,7 @@
       </c>
       <c r="H8" s="8">
         <f>+H5-H6+H7</f>
-        <v>13023.2570144</v>
+        <v>11125.633136000002</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -3636,10 +3667,18 @@
       <c r="J2" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="K2" s="100" t="s">
+        <v>385</v>
+      </c>
+      <c r="L2" s="100" t="s">
+        <v>386</v>
+      </c>
+      <c r="M2" s="100" t="s">
+        <v>387</v>
+      </c>
+      <c r="N2" s="100" t="s">
+        <v>388</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
@@ -3693,7 +3732,9 @@
         <f>+Model!J12-Quarters!I3</f>
         <v>964.50199999999995</v>
       </c>
-      <c r="K3" s="4"/>
+      <c r="K3" s="4">
+        <v>771.40800000000002</v>
+      </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -3750,7 +3791,9 @@
         <f>+Model!J13-Quarters!I4</f>
         <v>416.34399999999982</v>
       </c>
-      <c r="K4" s="4"/>
+      <c r="K4" s="4">
+        <v>358.08800000000002</v>
+      </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -3774,7 +3817,7 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="98" t="s">
+      <c r="B5" s="92" t="s">
         <v>383</v>
       </c>
       <c r="C5" s="24">
@@ -3803,7 +3846,9 @@
         <f>+Model!J14-Quarters!I5</f>
         <v>51.343000000000004</v>
       </c>
-      <c r="K5" s="4"/>
+      <c r="K5" s="4">
+        <v>101.94499999999999</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -3860,7 +3905,9 @@
         <f>+Model!J15-Quarters!I6</f>
         <v>10.865000000000004</v>
       </c>
-      <c r="K6" s="4"/>
+      <c r="K6" s="4">
+        <v>7.1749999999999998</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -3917,7 +3964,9 @@
         <f>+Model!J16-Quarters!I7</f>
         <v>12.209000000000001</v>
       </c>
-      <c r="K7" s="4"/>
+      <c r="K7" s="4">
+        <v>6.02</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -3974,7 +4023,9 @@
         <f>+Model!J17-Quarters!I8</f>
         <v>482.95500000000015</v>
       </c>
-      <c r="K8" s="4"/>
+      <c r="K8" s="4">
+        <v>461</v>
+      </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
@@ -4033,7 +4084,9 @@
         <f>+Model!J18-Quarters!I9</f>
         <v>425.70399999999995</v>
       </c>
-      <c r="K9" s="4"/>
+      <c r="K9" s="4">
+        <v>333</v>
+      </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
@@ -4092,7 +4145,9 @@
         <f>+Model!J19-Quarters!I10</f>
         <v>295.29300000000001</v>
       </c>
-      <c r="K10" s="4"/>
+      <c r="K10" s="4">
+        <v>256</v>
+      </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
@@ -4151,7 +4206,9 @@
         <f>+Model!J20-Quarters!I11</f>
         <v>181.94099999999997</v>
       </c>
-      <c r="K11" s="4"/>
+      <c r="K11" s="4">
+        <v>145</v>
+      </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
@@ -4210,7 +4267,9 @@
         <f>+Model!J21-Quarters!I12</f>
         <v>69.37</v>
       </c>
-      <c r="K12" s="4"/>
+      <c r="K12" s="4">
+        <v>49</v>
+      </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
@@ -4269,7 +4328,9 @@
         <f>+Model!J22-Quarters!I13</f>
         <v>1455.2629999999999</v>
       </c>
-      <c r="K13" s="4"/>
+      <c r="K13" s="4">
+        <v>1244.636</v>
+      </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
@@ -4328,7 +4389,9 @@
         <f>+Model!J23-Quarters!I14</f>
         <v>148.39299999999997</v>
       </c>
-      <c r="K14" s="4"/>
+      <c r="K14" s="4">
+        <v>129.39699999999999</v>
+      </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
@@ -4387,7 +4450,9 @@
         <f>+Model!J24-Quarters!I15</f>
         <v>44.214999999999989</v>
       </c>
-      <c r="K15" s="4"/>
+      <c r="K15" s="4">
+        <v>53.665999999999997</v>
+      </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
@@ -4448,7 +4513,9 @@
         <f t="shared" si="0"/>
         <v>1647.8709999999999</v>
       </c>
-      <c r="K16" s="22"/>
+      <c r="K16" s="22">
+        <v>1427.6990000000001</v>
+      </c>
       <c r="L16" s="22"/>
       <c r="M16" s="22"/>
       <c r="N16" s="22"/>
@@ -4509,16 +4576,33 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="B18" s="99" t="s">
+        <v>78</v>
+      </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
+      <c r="G18" s="28">
+        <f t="shared" ref="G18:I22" si="1">+G3/C3-1</f>
+        <v>1.210653753026536E-3</v>
+      </c>
+      <c r="H18" s="28">
+        <f t="shared" si="1"/>
+        <v>-7.0535147392290276E-2</v>
+      </c>
+      <c r="I18" s="28">
+        <f t="shared" si="1"/>
+        <v>-5.3336579433773901E-2</v>
+      </c>
+      <c r="J18" s="28">
+        <f>+J3/F3-1</f>
+        <v>-6.3381143362109982E-2</v>
+      </c>
+      <c r="K18" s="28">
+        <f>+K3/G3-1</f>
+        <v>-6.7221281741233319E-2</v>
+      </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
@@ -4544,16 +4628,33 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
+      <c r="B19" s="99" t="s">
+        <v>389</v>
+      </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
+      <c r="G19" s="28">
+        <f t="shared" si="1"/>
+        <v>0.61802575107296143</v>
+      </c>
+      <c r="H19" s="28">
+        <f t="shared" si="1"/>
+        <v>0.35737373737373734</v>
+      </c>
+      <c r="I19" s="28">
+        <f t="shared" si="1"/>
+        <v>0.22741020968801173</v>
+      </c>
+      <c r="J19" s="28">
+        <f t="shared" ref="J19:K22" si="2">+J4/F4-1</f>
+        <v>0.11407118812781913</v>
+      </c>
+      <c r="K19" s="28">
+        <f t="shared" si="2"/>
+        <v>-5.0164456233421695E-2</v>
+      </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
@@ -4579,16 +4680,33 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
+      <c r="B20" s="99" t="s">
+        <v>390</v>
+      </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
+      <c r="G20" s="28" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H20" s="28" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I20" s="28" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J20" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K20" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
@@ -4614,16 +4732,33 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
+      <c r="B21" s="99" t="s">
+        <v>391</v>
+      </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
+      <c r="G21" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="28">
+        <f t="shared" si="1"/>
+        <v>4.6249999999999902E-2</v>
+      </c>
+      <c r="I21" s="28">
+        <f t="shared" si="1"/>
+        <v>0.14432673115307826</v>
+      </c>
+      <c r="J21" s="28">
+        <f t="shared" si="2"/>
+        <v>7.0865365661344937E-2</v>
+      </c>
+      <c r="K21" s="28">
+        <f t="shared" si="2"/>
+        <v>2.4999999999999911E-2</v>
+      </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
@@ -4649,16 +4784,33 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
+      <c r="B22" s="99" t="s">
+        <v>81</v>
+      </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
+      <c r="G22" s="28">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="28">
+        <f t="shared" si="1"/>
+        <v>0.21660000000000013</v>
+      </c>
+      <c r="I22" s="28">
+        <f t="shared" si="1"/>
+        <v>0.14088240863472823</v>
+      </c>
+      <c r="J22" s="28">
+        <f t="shared" si="2"/>
+        <v>0.12639542393209724</v>
+      </c>
+      <c r="K22" s="28">
+        <f t="shared" si="2"/>
+        <v>0.20399999999999996</v>
+      </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
@@ -4684,16 +4836,33 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
+      <c r="B23" s="99" t="s">
+        <v>69</v>
+      </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
+      <c r="G23" s="30">
+        <f t="shared" ref="G23:I23" si="3">+G16/C16-1</f>
+        <v>0.13069139966273191</v>
+      </c>
+      <c r="H23" s="30">
+        <f t="shared" si="3"/>
+        <v>2.6713703019299428E-2</v>
+      </c>
+      <c r="I23" s="30">
+        <f t="shared" si="3"/>
+        <v>3.8423963083257018E-2</v>
+      </c>
+      <c r="J23" s="30">
+        <f>+J16/F16-1</f>
+        <v>2.8363974488586186E-2</v>
+      </c>
+      <c r="K23" s="30">
+        <f>+K16/G16-1</f>
+        <v>6.4652498135719716E-2</v>
+      </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
@@ -11888,8 +12057,8 @@
       <c r="I3" s="24">
         <v>426</v>
       </c>
-      <c r="J3" s="97">
-        <f>+S3</f>
+      <c r="J3" s="91">
+        <f t="shared" ref="J3:J8" si="0">+S3</f>
         <v>423</v>
       </c>
       <c r="K3" s="24"/>
@@ -11961,8 +12130,8 @@
       <c r="I4" s="24">
         <v>0</v>
       </c>
-      <c r="J4" s="97">
-        <f>+S4</f>
+      <c r="J4" s="91">
+        <f t="shared" si="0"/>
         <v>220</v>
       </c>
       <c r="K4" s="24"/>
@@ -12015,28 +12184,28 @@
       </c>
       <c r="C5" s="24"/>
       <c r="D5" s="24">
-        <f t="shared" ref="D5:D10" si="0">+P5</f>
+        <f t="shared" ref="D5:D10" si="1">+P5</f>
         <v>145</v>
       </c>
       <c r="E5" s="24">
         <v>141</v>
       </c>
       <c r="F5" s="24">
-        <f t="shared" ref="F5:F8" si="1">+Q5</f>
+        <f t="shared" ref="F5:F8" si="2">+Q5</f>
         <v>141</v>
       </c>
       <c r="G5" s="24">
         <v>139</v>
       </c>
       <c r="H5" s="24">
-        <f t="shared" ref="H5:H10" si="2">+R5</f>
+        <f t="shared" ref="H5:H10" si="3">+R5</f>
         <v>147</v>
       </c>
       <c r="I5" s="24">
         <v>156</v>
       </c>
-      <c r="J5" s="97">
-        <f>+S5</f>
+      <c r="J5" s="91">
+        <f t="shared" si="0"/>
         <v>162</v>
       </c>
       <c r="K5" s="24"/>
@@ -12089,28 +12258,28 @@
       </c>
       <c r="C6" s="24"/>
       <c r="D6" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="E6" s="24">
         <v>28</v>
       </c>
       <c r="F6" s="24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="G6" s="24">
         <v>28</v>
       </c>
       <c r="H6" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="I6" s="24">
         <v>28</v>
       </c>
-      <c r="J6" s="97">
-        <f>+S6</f>
+      <c r="J6" s="91">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="K6" s="24"/>
@@ -12163,28 +12332,28 @@
       </c>
       <c r="C7" s="24"/>
       <c r="D7" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E7" s="24">
         <v>2</v>
       </c>
       <c r="F7" s="24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="G7" s="24">
         <v>2</v>
       </c>
       <c r="H7" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="I7" s="24">
         <v>2</v>
       </c>
-      <c r="J7" s="97">
-        <f>+S7</f>
+      <c r="J7" s="91">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="K7" s="24"/>
@@ -12237,28 +12406,28 @@
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="E8" s="24">
         <v>7</v>
       </c>
       <c r="F8" s="24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="G8" s="24">
         <v>7</v>
       </c>
       <c r="H8" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="I8" s="24">
         <v>8</v>
       </c>
-      <c r="J8" s="97">
-        <f>+S8</f>
+      <c r="J8" s="91">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="K8" s="24"/>
@@ -12310,68 +12479,68 @@
         <v>60</v>
       </c>
       <c r="C9" s="24">
-        <f t="shared" ref="C9:S9" si="3">+SUM(C3:C8)</f>
+        <f t="shared" ref="C9:S9" si="4">+SUM(C3:C8)</f>
         <v>0</v>
       </c>
       <c r="D9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>612</v>
       </c>
       <c r="E9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>606</v>
       </c>
       <c r="F9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>606</v>
       </c>
       <c r="G9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>593</v>
       </c>
       <c r="H9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>609</v>
       </c>
       <c r="I9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>620</v>
       </c>
       <c r="J9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>843</v>
       </c>
       <c r="K9" s="24"/>
       <c r="L9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>636</v>
       </c>
       <c r="M9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>641</v>
       </c>
       <c r="N9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>633</v>
       </c>
       <c r="O9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>635</v>
       </c>
       <c r="P9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>612</v>
       </c>
       <c r="Q9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>606</v>
       </c>
       <c r="R9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>609</v>
       </c>
       <c r="S9" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>843</v>
       </c>
       <c r="T9" s="4"/>
@@ -12399,7 +12568,7 @@
       </c>
       <c r="C10" s="24"/>
       <c r="D10" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="E10" s="24">
@@ -12413,13 +12582,13 @@
         <v>24</v>
       </c>
       <c r="H10" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="I10" s="24">
         <v>22</v>
       </c>
-      <c r="J10" s="97">
+      <c r="J10" s="91">
         <f>+S10</f>
         <v>22</v>
       </c>
@@ -12529,7 +12698,7 @@
         <v>1646.788</v>
       </c>
       <c r="J12" s="25">
-        <f>+S12-I12</f>
+        <f t="shared" ref="J12:J24" si="5">+S12-I12</f>
         <v>1746.0729999999999</v>
       </c>
       <c r="K12" s="25"/>
@@ -12583,21 +12752,21 @@
         <v>285</v>
       </c>
       <c r="F13" s="25">
-        <f t="shared" ref="F13:F24" si="4">+Q13-E13</f>
+        <f t="shared" ref="F13:F24" si="6">+Q13-E13</f>
         <v>468.23400000000004</v>
       </c>
       <c r="G13" s="25">
         <v>530</v>
       </c>
       <c r="H13" s="25">
-        <f t="shared" ref="H13:H38" si="5">+R13-G13</f>
+        <f t="shared" ref="H13:H38" si="7">+R13-G13</f>
         <v>698.05300000000011</v>
       </c>
       <c r="I13" s="25">
         <v>780.14</v>
       </c>
       <c r="J13" s="25">
-        <f>+S13-I13</f>
+        <f t="shared" si="5"/>
         <v>814.44099999999992</v>
       </c>
       <c r="K13" s="25"/>
@@ -12667,7 +12836,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="25">
-        <f>+S14-I14</f>
+        <f t="shared" si="5"/>
         <v>51.343000000000004</v>
       </c>
       <c r="K14" s="25"/>
@@ -12721,21 +12890,21 @@
         <v>13</v>
       </c>
       <c r="F15" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>22.790999999999997</v>
       </c>
       <c r="G15" s="25">
         <v>15</v>
       </c>
       <c r="H15" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>16.658999999999999</v>
       </c>
       <c r="I15" s="25">
         <v>15.37</v>
       </c>
       <c r="J15" s="25">
-        <f>+S15-I15</f>
+        <f t="shared" si="5"/>
         <v>18.318000000000005</v>
       </c>
       <c r="K15" s="25"/>
@@ -12789,21 +12958,21 @@
         <v>9</v>
       </c>
       <c r="F16" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>16.077000000000002</v>
       </c>
       <c r="G16" s="25">
         <v>10</v>
       </c>
       <c r="H16" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>16.12</v>
       </c>
       <c r="I16" s="25">
         <v>11.083</v>
       </c>
       <c r="J16" s="25">
-        <f>+S16-I16</f>
+        <f t="shared" si="5"/>
         <v>18.234000000000002</v>
       </c>
       <c r="K16" s="25"/>
@@ -12862,21 +13031,21 @@
         <v>715.72400000000005</v>
       </c>
       <c r="F17" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>730.27599999999995</v>
       </c>
       <c r="G17" s="25">
         <v>774.43499999999995</v>
       </c>
       <c r="H17" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>829.97800000000007</v>
       </c>
       <c r="I17" s="25">
         <v>838.37099999999998</v>
       </c>
       <c r="J17" s="25">
-        <f>+S17-I17</f>
+        <f t="shared" si="5"/>
         <v>861.07700000000011</v>
       </c>
       <c r="K17" s="25"/>
@@ -12935,21 +13104,21 @@
         <v>582.11199999999997</v>
       </c>
       <c r="F18" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>729.88800000000003</v>
       </c>
       <c r="G18" s="25">
         <v>682.19200000000001</v>
       </c>
       <c r="H18" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>849.43000000000006</v>
       </c>
       <c r="I18" s="25">
         <v>727.56200000000001</v>
       </c>
       <c r="J18" s="25">
-        <f>+S18-I18</f>
+        <f t="shared" si="5"/>
         <v>835.23500000000001</v>
       </c>
       <c r="K18" s="25"/>
@@ -13008,21 +13177,21 @@
         <v>361.07299999999998</v>
       </c>
       <c r="F19" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>405.92700000000002</v>
       </c>
       <c r="G19" s="25">
         <v>386.96100000000001</v>
       </c>
       <c r="H19" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>442.84799999999996</v>
       </c>
       <c r="I19" s="25">
         <v>424.09</v>
       </c>
       <c r="J19" s="25">
-        <f>+S19-I19</f>
+        <f t="shared" si="5"/>
         <v>507.95700000000005</v>
       </c>
       <c r="K19" s="25"/>
@@ -13081,21 +13250,21 @@
         <v>223.58699999999999</v>
       </c>
       <c r="F20" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>260.41300000000001</v>
       </c>
       <c r="G20" s="25">
         <v>308.61200000000002</v>
       </c>
       <c r="H20" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>347.81900000000002</v>
       </c>
       <c r="I20" s="25">
         <v>325.94499999999999</v>
       </c>
       <c r="J20" s="25">
-        <f>+S20-I20</f>
+        <f t="shared" si="5"/>
         <v>330.15600000000001</v>
       </c>
       <c r="K20" s="25"/>
@@ -13154,21 +13323,21 @@
         <v>92.213999999999999</v>
       </c>
       <c r="F21" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>87.786000000000001</v>
       </c>
       <c r="G21" s="25">
         <v>110.39100000000001</v>
       </c>
       <c r="H21" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>116.54199999999999</v>
       </c>
       <c r="I21" s="25">
         <v>137.41300000000001</v>
       </c>
       <c r="J21" s="25">
-        <f>+S21-I21</f>
+        <f t="shared" si="5"/>
         <v>113.98399999999998</v>
       </c>
       <c r="K21" s="25"/>
@@ -13228,21 +13397,21 @@
         <v>1974.71</v>
       </c>
       <c r="F22" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2214.9660000000003</v>
       </c>
       <c r="G22" s="25">
         <v>2262.5909999999999</v>
       </c>
       <c r="H22" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2586.6169999999997</v>
       </c>
       <c r="I22" s="25">
         <v>2453.3809999999999</v>
       </c>
       <c r="J22" s="25">
-        <f>+S22-I22</f>
+        <f t="shared" si="5"/>
         <v>2648.4090000000001</v>
       </c>
       <c r="K22" s="25"/>
@@ -13301,21 +13470,21 @@
         <v>210.18600000000001</v>
       </c>
       <c r="F23" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>223.02</v>
       </c>
       <c r="G23" s="25">
         <v>225.21299999999999</v>
       </c>
       <c r="H23" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>235.60499999999999</v>
       </c>
       <c r="I23" s="25">
         <v>219.762</v>
       </c>
       <c r="J23" s="25">
-        <f>+S23-I23</f>
+        <f t="shared" si="5"/>
         <v>250.95999999999998</v>
       </c>
       <c r="K23" s="25"/>
@@ -13374,21 +13543,21 @@
         <v>47.482999999999997</v>
       </c>
       <c r="F24" s="25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>56.045999999999999</v>
       </c>
       <c r="G24" s="25">
         <v>60.83</v>
       </c>
       <c r="H24" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>60.701000000000008</v>
       </c>
       <c r="I24" s="25">
         <v>66.891999999999996</v>
       </c>
       <c r="J24" s="25">
-        <f>+S24-I24</f>
+        <f t="shared" si="5"/>
         <v>78.206999999999994</v>
       </c>
       <c r="K24" s="25"/>
@@ -13442,19 +13611,19 @@
         <v>22</v>
       </c>
       <c r="C25" s="26">
-        <f t="shared" ref="C25:F25" si="6">+SUM(C22:C24)</f>
+        <f t="shared" ref="C25:F25" si="8">+SUM(C22:C24)</f>
         <v>0</v>
       </c>
       <c r="D25" s="26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E25" s="26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2232.3790000000004</v>
       </c>
       <c r="F25" s="26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2494.0320000000002</v>
       </c>
       <c r="G25" s="26">
@@ -13462,44 +13631,44 @@
         <v>2548.634</v>
       </c>
       <c r="H25" s="26">
-        <f t="shared" ref="H25:R25" si="7">+SUM(H22:H24)</f>
+        <f t="shared" ref="H25:R25" si="9">+SUM(H22:H24)</f>
         <v>2882.9229999999998</v>
       </c>
       <c r="I25" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2740.0349999999999</v>
       </c>
       <c r="J25" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2977.576</v>
       </c>
       <c r="K25" s="26"/>
       <c r="L25" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>3142.1479999999997</v>
       </c>
       <c r="M25" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>3225.5940000000001</v>
       </c>
       <c r="N25" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>2422.739</v>
       </c>
       <c r="O25" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>3365.6670000000004</v>
       </c>
       <c r="P25" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4200.674</v>
       </c>
       <c r="Q25" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4726.4110000000001</v>
       </c>
       <c r="R25" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5431.5569999999998</v>
       </c>
       <c r="S25" s="26">
@@ -13543,7 +13712,7 @@
         <v>514.673</v>
       </c>
       <c r="H26" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>580.19200000000001</v>
       </c>
       <c r="I26" s="8">
@@ -13604,56 +13773,56 @@
         <v>24</v>
       </c>
       <c r="C27" s="8">
-        <f t="shared" ref="C27:J27" si="8">C25-C26</f>
+        <f t="shared" ref="C27:J27" si="10">C25-C26</f>
         <v>0</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E27" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1793.3950000000004</v>
       </c>
       <c r="F27" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2008.3760000000002</v>
       </c>
       <c r="G27" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2033.961</v>
       </c>
       <c r="H27" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2302.7309999999998</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2194.5819999999999</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2397.585</v>
       </c>
       <c r="K27" s="8"/>
       <c r="L27" s="8">
-        <f t="shared" ref="L27:P27" si="9">+L25-L26</f>
+        <f t="shared" ref="L27:P27" si="11">+L25-L26</f>
         <v>2262.58</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2319.6120000000001</v>
       </c>
       <c r="N27" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1743.3780000000002</v>
       </c>
       <c r="O27" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2547.3580000000002</v>
       </c>
       <c r="P27" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>3312.0940000000001</v>
       </c>
       <c r="Q27" s="8">
@@ -13661,11 +13830,11 @@
         <v>3801.7710000000002</v>
       </c>
       <c r="R27" s="8">
-        <f t="shared" ref="R27:S27" si="10">+R25-R26</f>
+        <f t="shared" ref="R27:S27" si="12">+R25-R26</f>
         <v>4336.692</v>
       </c>
       <c r="S27" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>4592.0769999999993</v>
       </c>
       <c r="T27" s="4"/>
@@ -13706,7 +13875,7 @@
         <v>978.47</v>
       </c>
       <c r="H28" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1104.2819999999999</v>
       </c>
       <c r="I28" s="8">
@@ -13779,7 +13948,7 @@
         <v>219.25</v>
       </c>
       <c r="H29" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>253.84500000000003</v>
       </c>
       <c r="I29" s="8">
@@ -13852,7 +14021,7 @@
         <v>81.659000000000006</v>
       </c>
       <c r="H30" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>76.424999999999997</v>
       </c>
       <c r="I30" s="8">
@@ -13925,7 +14094,7 @@
         <v>179.46299999999999</v>
       </c>
       <c r="H31" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>163.74800000000002</v>
       </c>
       <c r="I31" s="8">
@@ -13988,19 +14157,19 @@
         <v>47</v>
       </c>
       <c r="C32" s="8">
-        <f t="shared" ref="C32:F32" si="11">+C27-SUM(C28:C31)</f>
+        <f t="shared" ref="C32:F32" si="13">+C27-SUM(C28:C31)</f>
         <v>0</v>
       </c>
       <c r="D32" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E32" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>491.41900000000055</v>
       </c>
       <c r="F32" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>570.27300000000037</v>
       </c>
       <c r="G32" s="8">
@@ -14008,48 +14177,48 @@
         <v>575.11899999999991</v>
       </c>
       <c r="H32" s="8">
-        <f t="shared" ref="H32:S32" si="12">+H27-SUM(H28:H31)</f>
+        <f t="shared" ref="H32:S32" si="14">+H27-SUM(H28:H31)</f>
         <v>704.43099999999981</v>
       </c>
       <c r="I32" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>607.29399999999987</v>
       </c>
       <c r="J32" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>691.83600000000001</v>
       </c>
       <c r="K32" s="8"/>
       <c r="L32" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>323.83199999999988</v>
       </c>
       <c r="M32" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>306.779</v>
       </c>
       <c r="N32" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>20.061000000000149</v>
       </c>
       <c r="O32" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>489.48400000000038</v>
       </c>
       <c r="P32" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>845.17600000000039</v>
       </c>
       <c r="Q32" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1061.6920000000005</v>
       </c>
       <c r="R32" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1279.5500000000002</v>
       </c>
       <c r="S32" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1299.0399999999995</v>
       </c>
       <c r="T32" s="4"/>
@@ -14090,7 +14259,7 @@
         <v>-38.090000000000003</v>
       </c>
       <c r="H33" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>-52.736999999999995</v>
       </c>
       <c r="I33" s="8">
@@ -14165,7 +14334,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I34" s="8">
@@ -14226,19 +14395,19 @@
         <v>27</v>
       </c>
       <c r="C35" s="8">
-        <f t="shared" ref="C35:F35" si="13">+C32+C33+C34</f>
+        <f t="shared" ref="C35:F35" si="15">+C32+C33+C34</f>
         <v>0</v>
       </c>
       <c r="D35" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E35" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>445.01100000000054</v>
       </c>
       <c r="F35" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>526.45200000000034</v>
       </c>
       <c r="G35" s="8">
@@ -14246,48 +14415,48 @@
         <v>537.02899999999988</v>
       </c>
       <c r="H35" s="8">
-        <f t="shared" ref="H35:S35" si="14">+H32+H33+H34</f>
+        <f t="shared" ref="H35:S35" si="16">+H32+H33+H34</f>
         <v>651.69399999999985</v>
       </c>
       <c r="I35" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>557.91499999999985</v>
       </c>
       <c r="J35" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>643.45900000000006</v>
       </c>
       <c r="K35" s="8"/>
       <c r="L35" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>302.52399999999989</v>
       </c>
       <c r="M35" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>234.76</v>
       </c>
       <c r="N35" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-51.811999999999856</v>
       </c>
       <c r="O35" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>421.65500000000037</v>
       </c>
       <c r="P35" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>710.97500000000036</v>
       </c>
       <c r="Q35" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>971.46300000000042</v>
       </c>
       <c r="R35" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1188.7230000000002</v>
       </c>
       <c r="S35" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1201.2839999999994</v>
       </c>
       <c r="T35" s="4"/>
@@ -14328,7 +14497,7 @@
         <v>151.316</v>
       </c>
       <c r="H36" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>194.00699999999998</v>
       </c>
       <c r="I36" s="8">
@@ -14389,19 +14558,19 @@
         <v>29</v>
       </c>
       <c r="C37" s="8">
-        <f t="shared" ref="C37:F37" si="15">+C35-C36</f>
+        <f t="shared" ref="C37:F37" si="17">+C35-C36</f>
         <v>0</v>
       </c>
       <c r="D37" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="E37" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>306.63000000000056</v>
       </c>
       <c r="F37" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>366.76200000000028</v>
       </c>
       <c r="G37" s="8">
@@ -14409,48 +14578,48 @@
         <v>385.71299999999985</v>
       </c>
       <c r="H37" s="8">
-        <f t="shared" ref="H37" si="16">+H35-H36</f>
+        <f t="shared" ref="H37" si="18">+H35-H36</f>
         <v>457.6869999999999</v>
       </c>
       <c r="I37" s="8">
-        <f t="shared" ref="I37" si="17">+I35-I36</f>
+        <f t="shared" ref="I37" si="19">+I35-I36</f>
         <v>386.99199999999985</v>
       </c>
       <c r="J37" s="8">
-        <f t="shared" ref="J37:S37" si="18">+J35-J36</f>
+        <f t="shared" ref="J37:S37" si="20">+J35-J36</f>
         <v>468.02000000000004</v>
       </c>
       <c r="K37" s="8"/>
       <c r="L37" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>208.16799999999989</v>
       </c>
       <c r="M37" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>257.72399999999999</v>
       </c>
       <c r="N37" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-54.367999999999853</v>
       </c>
       <c r="O37" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>295.10300000000035</v>
       </c>
       <c r="P37" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>469.15500000000037</v>
       </c>
       <c r="Q37" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>673.39200000000039</v>
       </c>
       <c r="R37" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>843.4000000000002</v>
       </c>
       <c r="S37" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>854.92199999999934</v>
       </c>
       <c r="T37" s="4"/>
@@ -14491,7 +14660,7 @@
         <v>2.214</v>
       </c>
       <c r="H38" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2.2790000000000004</v>
       </c>
       <c r="I38" s="8">
@@ -14552,19 +14721,19 @@
         <v>31</v>
       </c>
       <c r="C39" s="8">
-        <f t="shared" ref="C39:F39" si="19">+C37-C38</f>
+        <f t="shared" ref="C39:F39" si="21">+C37-C38</f>
         <v>0</v>
       </c>
       <c r="D39" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="E39" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>305.16800000000057</v>
       </c>
       <c r="F39" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>365.85800000000029</v>
       </c>
       <c r="G39" s="8">
@@ -14572,48 +14741,48 @@
         <v>383.49899999999985</v>
       </c>
       <c r="H39" s="8">
-        <f t="shared" ref="H39" si="20">+H37-H38</f>
+        <f t="shared" ref="H39" si="22">+H37-H38</f>
         <v>455.4079999999999</v>
       </c>
       <c r="I39" s="8">
-        <f t="shared" ref="I39" si="21">+I37-I38</f>
+        <f t="shared" ref="I39" si="23">+I37-I38</f>
         <v>385.88299999999987</v>
       </c>
       <c r="J39" s="8">
-        <f t="shared" ref="J39:S39" si="22">+J37-J38</f>
+        <f t="shared" ref="J39:S39" si="24">+J37-J38</f>
         <v>466.14300000000003</v>
       </c>
       <c r="K39" s="8"/>
       <c r="L39" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>205.42899999999989</v>
       </c>
       <c r="M39" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>255.78799999999998</v>
       </c>
       <c r="N39" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-54.138999999999854</v>
       </c>
       <c r="O39" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>294.25400000000036</v>
       </c>
       <c r="P39" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>465.19300000000038</v>
       </c>
       <c r="Q39" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>671.02600000000041</v>
       </c>
       <c r="R39" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>838.90700000000015</v>
       </c>
       <c r="S39" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>851.93599999999935</v>
       </c>
       <c r="T39" s="4"/>
@@ -14682,19 +14851,19 @@
         <v>1</v>
       </c>
       <c r="C41" s="27">
-        <f t="shared" ref="C41:F41" si="23">+C39/C42</f>
+        <f t="shared" ref="C41:F41" si="25">+C39/C42</f>
         <v>0</v>
       </c>
       <c r="D41" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E41" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.11926103553820058</v>
       </c>
       <c r="F41" s="27">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.14297896221076567</v>
       </c>
       <c r="G41" s="27">
@@ -14702,7 +14871,7 @@
         <v>0.14987314485091582</v>
       </c>
       <c r="H41" s="27">
-        <f t="shared" ref="H41:J41" si="24">+H39/H42</f>
+        <f t="shared" ref="H41:J41" si="26">+H39/H42</f>
         <v>0.17797550749875721</v>
       </c>
       <c r="I41" s="27">
@@ -14710,28 +14879,28 @@
         <v>0.15080482284049229</v>
       </c>
       <c r="J41" s="27">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.18217079408353212</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="27">
-        <f t="shared" ref="L41:P41" si="25">+L39/L42</f>
+        <f t="shared" ref="L41:P41" si="27">+L39/L42</f>
         <v>8.0282582936536423E-2</v>
       </c>
       <c r="M41" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>9.9963108052761734E-2</v>
       </c>
       <c r="N41" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-2.1157766223859027E-2</v>
       </c>
       <c r="O41" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.11499579494330221</v>
       </c>
       <c r="P41" s="27">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.18179952978399466</v>
       </c>
       <c r="Q41" s="27">
@@ -14889,57 +15058,57 @@
       <c r="C44" s="28"/>
       <c r="D44" s="28"/>
       <c r="E44" s="28" t="e">
-        <f t="shared" ref="E44:J45" si="26">+E9/C9-1</f>
+        <f t="shared" ref="E44:J45" si="28">+E9/C9-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F44" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-9.8039215686274161E-3</v>
       </c>
       <c r="G44" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-2.1452145214521434E-2</v>
       </c>
       <c r="H44" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4.9504950495049549E-3</v>
       </c>
       <c r="I44" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4.5531197301855064E-2</v>
       </c>
       <c r="J44" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0.38423645320197042</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
       <c r="M44" s="29">
-        <f t="shared" ref="M44:S45" si="27">+M9/L9-1</f>
+        <f t="shared" ref="M44:S45" si="29">+M9/L9-1</f>
         <v>7.8616352201257289E-3</v>
       </c>
       <c r="N44" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-1.2480499219968744E-2</v>
       </c>
       <c r="O44" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>3.1595576619274368E-3</v>
       </c>
       <c r="P44" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-3.622047244094484E-2</v>
       </c>
       <c r="Q44" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-9.8039215686274161E-3</v>
       </c>
       <c r="R44" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>4.9504950495049549E-3</v>
       </c>
       <c r="S44" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.38423645320197042</v>
       </c>
       <c r="T44" s="4"/>
@@ -14970,57 +15139,57 @@
       <c r="C45" s="28"/>
       <c r="D45" s="28"/>
       <c r="E45" s="28" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F45" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-3.8461538461538436E-2</v>
       </c>
       <c r="G45" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-4.0000000000000036E-2</v>
       </c>
       <c r="H45" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-7.999999999999996E-2</v>
       </c>
       <c r="I45" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-8.333333333333337E-2</v>
       </c>
       <c r="J45" s="28">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>-4.3478260869565188E-2</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-0.26470588235294112</v>
       </c>
       <c r="N45" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="O45" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="P45" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="Q45" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-3.8461538461538436E-2</v>
       </c>
       <c r="R45" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-7.999999999999996E-2</v>
       </c>
       <c r="S45" s="29">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-4.3478260869565188E-2</v>
       </c>
       <c r="T45" s="4"/>
@@ -15051,57 +15220,57 @@
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="28" t="e">
-        <f t="shared" ref="E46:J47" si="28">+E12/C12-1</f>
+        <f t="shared" ref="E46:J47" si="30">+E12/C12-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F46" s="28" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G46" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>2.3980815347721895E-2</v>
       </c>
       <c r="H46" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-0.17329743809787335</v>
       </c>
       <c r="I46" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-3.5838407494145241E-2</v>
       </c>
       <c r="J46" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-5.8911509041833177E-2</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
       <c r="M46" s="29">
-        <f t="shared" ref="M46:S47" si="29">+M12/L12-1</f>
+        <f t="shared" ref="M46:S47" si="31">+M12/L12-1</f>
         <v>3.3321501672329612E-2</v>
       </c>
       <c r="N46" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>-0.23860952095599974</v>
       </c>
       <c r="O46" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.41988701294829633</v>
       </c>
       <c r="P46" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.27648596262789593</v>
       </c>
       <c r="Q46" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>7.2510454917409373E-2</v>
       </c>
       <c r="R46" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>-8.9188507349496127E-2</v>
       </c>
       <c r="S46" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>-4.7852093071289792E-2</v>
       </c>
       <c r="T46" s="4"/>
@@ -15132,57 +15301,57 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="28" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F47" s="28" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G47" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.85964912280701755</v>
       </c>
       <c r="H47" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.49082082890178858</v>
       </c>
       <c r="I47" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.47196226415094333</v>
       </c>
       <c r="J47" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.16673232548244865</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>-6.5824872760631425E-3</v>
       </c>
       <c r="N47" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>-0.26858250220315161</v>
       </c>
       <c r="O47" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.21767117758280041</v>
       </c>
       <c r="P47" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.21866611501449329</v>
       </c>
       <c r="Q47" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.54050704363618518</v>
       </c>
       <c r="R47" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.63037382805343367</v>
       </c>
       <c r="S47" s="29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.29846268849960045</v>
       </c>
       <c r="T47" s="4"/>
@@ -15287,57 +15456,57 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="28" t="e">
-        <f t="shared" ref="E49:E59" si="30">+E15/C15-1</f>
+        <f t="shared" ref="E49:E59" si="32">+E15/C15-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F49" s="28" t="e">
-        <f t="shared" ref="F49:F59" si="31">+F15/D15-1</f>
+        <f t="shared" ref="F49:F59" si="33">+F15/D15-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G49" s="28">
-        <f t="shared" ref="G49:G59" si="32">+G15/E15-1</f>
+        <f t="shared" ref="G49:G59" si="34">+G15/E15-1</f>
         <v>0.15384615384615374</v>
       </c>
       <c r="H49" s="28">
-        <f t="shared" ref="H49:H59" si="33">+H15/F15-1</f>
+        <f t="shared" ref="H49:H59" si="35">+H15/F15-1</f>
         <v>-0.26905357377912331</v>
       </c>
       <c r="I49" s="28">
-        <f t="shared" ref="I49:I59" si="34">+I15/G15-1</f>
+        <f t="shared" ref="I49:I59" si="36">+I15/G15-1</f>
         <v>2.4666666666666615E-2</v>
       </c>
       <c r="J49" s="28">
-        <f t="shared" ref="J49:J59" si="35">+J15/H15-1</f>
+        <f t="shared" ref="J49:J59" si="37">+J15/H15-1</f>
         <v>9.9585809472357623E-2</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="29">
-        <f t="shared" ref="M49:S59" si="36">+M15/L15-1</f>
+        <f t="shared" ref="M49:S59" si="38">+M15/L15-1</f>
         <v>1.0451801560532159E-2</v>
       </c>
       <c r="N49" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.47043738628386411</v>
       </c>
       <c r="O49" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>6.9987014392381974E-2</v>
       </c>
       <c r="P49" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>6.1186822077823333E-2</v>
       </c>
       <c r="Q49" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.14724452598222582</v>
       </c>
       <c r="R49" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.11544801765807045</v>
       </c>
       <c r="S49" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>6.4089200543289593E-2</v>
       </c>
       <c r="T49" s="4"/>
@@ -15368,57 +15537,57 @@
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="28" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F50" s="28" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G50" s="28">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.11111111111111116</v>
       </c>
       <c r="H50" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>2.6746283510605817E-3</v>
       </c>
       <c r="I50" s="28">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.10830000000000006</v>
       </c>
       <c r="J50" s="28">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.13114143920595533</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.13180120654984195</v>
       </c>
       <c r="N50" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.40174628153713388</v>
       </c>
       <c r="O50" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.5406873143826898</v>
       </c>
       <c r="P50" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.20867984799250983</v>
       </c>
       <c r="Q50" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.14266836781190184</v>
       </c>
       <c r="R50" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>4.1591896957371199E-2</v>
       </c>
       <c r="S50" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.12239663093414999</v>
       </c>
       <c r="T50" s="4"/>
@@ -15449,57 +15618,57 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="28" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F51" s="28" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G51" s="28">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>8.2030223941072178E-2</v>
       </c>
       <c r="H51" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.13652646396704826</v>
       </c>
       <c r="I51" s="28">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.2558252145112254E-2</v>
       </c>
       <c r="J51" s="28">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3.7469667870714707E-2</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3.2450095686179514E-2</v>
       </c>
       <c r="N51" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.39668782363279509</v>
       </c>
       <c r="O51" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.30966860109751182</v>
       </c>
       <c r="P51" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.26927086982143678</v>
       </c>
       <c r="Q51" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.17370129870129869</v>
       </c>
       <c r="R51" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.1095525587828492</v>
       </c>
       <c r="S51" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>5.9233501598404015E-2</v>
       </c>
       <c r="T51" s="4"/>
@@ -15530,57 +15699,57 @@
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="28" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F52" s="28" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G52" s="28">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.17192567753284593</v>
       </c>
       <c r="H52" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.16378129247226969</v>
       </c>
       <c r="I52" s="28">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>6.6506203532143537E-2</v>
       </c>
       <c r="J52" s="28">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-1.671120633836809E-2</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-1.6876300044151971E-2</v>
       </c>
       <c r="N52" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-5.2818759563007966E-2</v>
       </c>
       <c r="O52" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.32026830040099807</v>
       </c>
       <c r="P52" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-6.7215492866988358E-2</v>
       </c>
       <c r="Q52" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.10530749789384997</v>
       </c>
       <c r="R52" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.16739481707317072</v>
       </c>
       <c r="S52" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2.0354238839609184E-2</v>
       </c>
       <c r="T52" s="4"/>
@@ -15611,57 +15780,57 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="28" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F53" s="28" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G53" s="28">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>7.169741298850929E-2</v>
       </c>
       <c r="H53" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>9.0954777583161395E-2</v>
       </c>
       <c r="I53" s="28">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>9.5950237879269373E-2</v>
       </c>
       <c r="J53" s="28">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.14702335790158272</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
       <c r="M53" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>6.8557242881009062E-2</v>
       </c>
       <c r="N53" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.28748885599975404</v>
       </c>
       <c r="O53" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.96303304682275281</v>
       </c>
       <c r="P53" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.227700824066704</v>
       </c>
       <c r="Q53" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-1.9181585677749413E-2</v>
       </c>
       <c r="R53" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>8.1889178617992053E-2</v>
       </c>
       <c r="S53" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.12320666563028371</v>
       </c>
       <c r="T53" s="4"/>
@@ -15692,57 +15861,57 @@
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="28" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F54" s="28" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G54" s="28">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.38027702862867718</v>
       </c>
       <c r="H54" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.33564376586422329</v>
       </c>
       <c r="I54" s="28">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>5.6164374684069207E-2</v>
       </c>
       <c r="J54" s="28">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-5.0782159686503681E-2</v>
       </c>
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
       <c r="M54" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.10202875714004334</v>
       </c>
       <c r="N54" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.27411379207625852</v>
       </c>
       <c r="O54" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.10517000199834414</v>
       </c>
       <c r="P54" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.1914602329966677</v>
       </c>
       <c r="Q54" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.31165311653116534</v>
       </c>
       <c r="R54" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.35626239669421489</v>
       </c>
       <c r="S54" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-5.027184883102942E-4</v>
       </c>
       <c r="T54" s="2"/>
@@ -15768,57 +15937,57 @@
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="28" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F55" s="28" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G55" s="28">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.19711757433795318</v>
       </c>
       <c r="H55" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.32756931629189157</v>
       </c>
       <c r="I55" s="28">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.24478444800753696</v>
       </c>
       <c r="J55" s="28">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>-2.1949168540097208E-2</v>
       </c>
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
       <c r="M55" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-1.2432382114746066E-2</v>
       </c>
       <c r="N55" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.14978896324923274</v>
       </c>
       <c r="O55" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.56175858288473601</v>
       </c>
       <c r="P55" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.31722168762127123</v>
       </c>
       <c r="Q55" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>7.7844311377245567E-2</v>
       </c>
       <c r="R55" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.26073888888888885</v>
       </c>
       <c r="S55" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.10780274354104513</v>
       </c>
       <c r="T55" s="2"/>
@@ -15844,57 +16013,57 @@
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
       <c r="E56" s="28" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F56" s="28" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G56" s="28">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.14578393789467814</v>
       </c>
       <c r="H56" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.16779083742143186</v>
       </c>
       <c r="I56" s="28">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>8.432368024092729E-2</v>
       </c>
       <c r="J56" s="28">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>2.388911848951758E-2</v>
       </c>
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
       <c r="M56" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>4.1110914516722774E-2</v>
       </c>
       <c r="N56" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.19753711642629246</v>
       </c>
       <c r="O56" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.38550513621730498</v>
       </c>
       <c r="P56" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.27504421916327515</v>
       </c>
       <c r="Q56" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.12114222989688717</v>
       </c>
       <c r="R56" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.15741837793662317</v>
       </c>
       <c r="S56" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>5.2087268683875809E-2</v>
       </c>
       <c r="T56" s="2"/>
@@ -15920,57 +16089,57 @@
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="28" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F57" s="28" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G57" s="28">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>7.1493819759641308E-2</v>
       </c>
       <c r="H57" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>5.6429916599407992E-2</v>
       </c>
       <c r="I57" s="28">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-2.4203753779755144E-2</v>
       </c>
       <c r="J57" s="28">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>6.5172640648543112E-2</v>
       </c>
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
       <c r="M57" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-3.3250657169507369E-2</v>
       </c>
       <c r="N57" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.49657372789369236</v>
       </c>
       <c r="O57" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.40025263524697285</v>
       </c>
       <c r="P57" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>4.8138239960182627E-3</v>
       </c>
       <c r="Q57" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.11760198750841688</v>
       </c>
       <c r="R57" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>6.373872938047942E-2</v>
       </c>
       <c r="S57" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2.1492216015867482E-2</v>
       </c>
       <c r="T57" s="2"/>
@@ -15996,57 +16165,57 @@
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
       <c r="E58" s="28" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F58" s="28" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G58" s="28">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.2810900743423963</v>
       </c>
       <c r="H58" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>8.3056774792135135E-2</v>
       </c>
       <c r="I58" s="28">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>9.9654775604142598E-2</v>
       </c>
       <c r="J58" s="28">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.2883972257458689</v>
       </c>
       <c r="K58" s="8"/>
       <c r="L58" s="8"/>
       <c r="M58" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-4.1401996370235894E-2</v>
       </c>
       <c r="N58" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.24569873387764762</v>
       </c>
       <c r="O58" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.53882596555077944</v>
       </c>
       <c r="P58" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.55120598609497007</v>
       </c>
       <c r="Q58" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.36075550064404194</v>
       </c>
       <c r="R58" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.17388364612813811</v>
       </c>
       <c r="S58" s="29">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.19392582962371718</v>
       </c>
       <c r="T58" s="2"/>
@@ -16072,57 +16241,57 @@
       <c r="C59" s="26"/>
       <c r="D59" s="26"/>
       <c r="E59" s="30" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F59" s="30" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G59" s="30">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.14166725273799807</v>
       </c>
       <c r="H59" s="30">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.15592863283229708</v>
       </c>
       <c r="I59" s="30">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>7.5099445428413736E-2</v>
       </c>
       <c r="J59" s="30">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>3.2832302492990628E-2</v>
       </c>
       <c r="K59" s="26"/>
       <c r="L59" s="26"/>
       <c r="M59" s="31">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2.6556992223154552E-2</v>
       </c>
       <c r="N59" s="31">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-0.24890144264901282</v>
       </c>
       <c r="O59" s="31">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.38919916672823618</v>
       </c>
       <c r="P59" s="31">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.24809554837124392</v>
       </c>
       <c r="Q59" s="31">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.1251553917299939</v>
       </c>
       <c r="R59" s="31">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.149192696107046</v>
       </c>
       <c r="S59" s="31">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>5.2648623589883981E-2</v>
       </c>
       <c r="T59" s="2"/>
@@ -16146,19 +16315,19 @@
         <v>82</v>
       </c>
       <c r="C60" s="28" t="e">
-        <f t="shared" ref="C60:F60" si="37">+C27/C25</f>
+        <f t="shared" ref="C60:F60" si="39">+C27/C25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D60" s="28" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E60" s="28">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0.80335597136507741</v>
       </c>
       <c r="F60" s="28">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0.80527274710188168</v>
       </c>
       <c r="G60" s="28">
@@ -16166,45 +16335,45 @@
         <v>0.79805927410526578</v>
       </c>
       <c r="H60" s="28">
-        <f t="shared" ref="H60:J60" si="38">+H27/H25</f>
+        <f t="shared" ref="H60:J60" si="40">+H27/H25</f>
         <v>0.79874870053761404</v>
       </c>
       <c r="I60" s="28">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.80093210488187194</v>
       </c>
       <c r="J60" s="28">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.80521370403307924</v>
       </c>
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
       <c r="M60" s="29">
-        <f t="shared" ref="M60:R60" si="39">+M27/M25</f>
+        <f t="shared" ref="M60:R60" si="41">+M27/M25</f>
         <v>0.71912708170960138</v>
       </c>
       <c r="N60" s="29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.71958968753959884</v>
       </c>
       <c r="O60" s="29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.75686572676381825</v>
       </c>
       <c r="P60" s="29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.78846727929851257</v>
       </c>
       <c r="Q60" s="29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.80436741536019618</v>
       </c>
       <c r="R60" s="29">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0.79842520293904684</v>
       </c>
       <c r="S60" s="29">
-        <f t="shared" ref="S60" si="40">+S27/S25</f>
+        <f t="shared" ref="S60" si="42">+S27/S25</f>
         <v>0.80315874659664555</v>
       </c>
       <c r="T60" s="2"/>
@@ -16228,19 +16397,19 @@
         <v>83</v>
       </c>
       <c r="C61" s="28" t="e">
-        <f t="shared" ref="C61:F61" si="41">+C32/C25</f>
+        <f t="shared" ref="C61:F61" si="43">+C32/C25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D61" s="28" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E61" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.22013242375062678</v>
       </c>
       <c r="F61" s="28">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.22865504532419806</v>
       </c>
       <c r="G61" s="28">
@@ -16248,45 +16417,45 @@
         <v>0.22565774450156434</v>
       </c>
       <c r="H61" s="28">
-        <f t="shared" ref="H61:J61" si="42">+H32/H25</f>
+        <f t="shared" ref="H61:J61" si="44">+H32/H25</f>
         <v>0.24434610289626185</v>
       </c>
       <c r="I61" s="28">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0.22163731485181756</v>
       </c>
       <c r="J61" s="28">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0.23234872930195569</v>
       </c>
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
       <c r="M61" s="29">
-        <f t="shared" ref="M61:R61" si="43">+M32/M25</f>
+        <f t="shared" ref="M61:R61" si="45">+M32/M25</f>
         <v>9.5107753796665043E-2</v>
       </c>
       <c r="N61" s="29">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>8.2802976300790747E-3</v>
       </c>
       <c r="O61" s="29">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.14543447108700899</v>
       </c>
       <c r="P61" s="29">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.20120009312791243</v>
       </c>
       <c r="Q61" s="29">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.22462963969912911</v>
       </c>
       <c r="R61" s="29">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.23557701778698084</v>
       </c>
       <c r="S61" s="29">
-        <f t="shared" ref="S61" si="44">+S32/S25</f>
+        <f t="shared" ref="S61" si="46">+S32/S25</f>
         <v>0.22720336313587647</v>
       </c>
       <c r="T61" s="2"/>
@@ -16310,19 +16479,19 @@
         <v>84</v>
       </c>
       <c r="C62" s="28" t="e">
-        <f t="shared" ref="C62:F62" si="45">+C36/C35</f>
+        <f t="shared" ref="C62:F62" si="47">+C36/C35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D62" s="28" t="e">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E62" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.3109608526530801</v>
       </c>
       <c r="F62" s="28">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>0.30333249754963398</v>
       </c>
       <c r="G62" s="28">
@@ -16330,45 +16499,45 @@
         <v>0.28176504434583616</v>
       </c>
       <c r="H62" s="28">
-        <f t="shared" ref="H62:J62" si="46">+H36/H35</f>
+        <f t="shared" ref="H62:J62" si="48">+H36/H35</f>
         <v>0.29769646490530838</v>
       </c>
       <c r="I62" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.30636028785746944</v>
       </c>
       <c r="J62" s="28">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.2726498502624099</v>
       </c>
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
       <c r="M62" s="29">
-        <f t="shared" ref="M62:R62" si="47">+M36/M35</f>
+        <f t="shared" ref="M62:R62" si="49">+M36/M35</f>
         <v>-9.7819049241778838E-2</v>
       </c>
       <c r="N62" s="29">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-4.9332201034509519E-2</v>
       </c>
       <c r="O62" s="29">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.30013162419513556</v>
       </c>
       <c r="P62" s="29">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.34012447695066617</v>
       </c>
       <c r="Q62" s="29">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.30682691981063603</v>
       </c>
       <c r="R62" s="29">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.29049913226209967</v>
       </c>
       <c r="S62" s="29">
-        <f t="shared" ref="S62" si="48">+S36/S35</f>
+        <f t="shared" ref="S62" si="50">+S36/S35</f>
         <v>0.28832649065499932</v>
       </c>
       <c r="T62" s="2"/>
@@ -17191,27 +17360,27 @@
       <c r="J71" s="8"/>
       <c r="K71" s="8"/>
       <c r="L71" s="8">
-        <f t="shared" ref="L71:Q71" si="49">+SUM(L65:L70)</f>
+        <f t="shared" ref="L71:Q71" si="51">+SUM(L65:L70)</f>
         <v>0</v>
       </c>
       <c r="M71" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>1566.0409020000002</v>
       </c>
       <c r="N71" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>1346.8670849999999</v>
       </c>
       <c r="O71" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>2169.835</v>
       </c>
       <c r="P71" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>2424.7670000000003</v>
       </c>
       <c r="Q71" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>2162.748</v>
       </c>
       <c r="R71" s="8">
@@ -18282,27 +18451,27 @@
       <c r="J80" s="8"/>
       <c r="K80" s="8"/>
       <c r="L80" s="8">
-        <f t="shared" ref="L80:Q80" si="50">+SUM(L72:L79)</f>
+        <f t="shared" ref="L80:Q80" si="52">+SUM(L72:L79)</f>
         <v>0</v>
       </c>
       <c r="M80" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>2572.287198</v>
       </c>
       <c r="N80" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>2515.7112690000004</v>
       </c>
       <c r="O80" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>4789.1759999999995</v>
       </c>
       <c r="P80" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>4952.8110000000006</v>
       </c>
       <c r="Q80" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>5452.3029999999999</v>
       </c>
       <c r="R80" s="8">
@@ -18412,19 +18581,19 @@
       <c r="J81" s="26"/>
       <c r="K81" s="26"/>
       <c r="L81" s="26">
-        <f t="shared" ref="L81:O81" si="51">+L80+L71</f>
+        <f t="shared" ref="L81:O81" si="53">+L80+L71</f>
         <v>0</v>
       </c>
       <c r="M81" s="26">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>4138.3281000000006</v>
       </c>
       <c r="N81" s="26">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>3862.5783540000002</v>
       </c>
       <c r="O81" s="26">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>6959.0109999999995</v>
       </c>
       <c r="P81" s="26">
@@ -19383,27 +19552,27 @@
       <c r="J89" s="8"/>
       <c r="K89" s="8"/>
       <c r="L89" s="8">
-        <f t="shared" ref="L89:Q89" si="52">+SUM(L82:L88)</f>
+        <f t="shared" ref="L89:Q89" si="54">+SUM(L82:L88)</f>
         <v>0</v>
       </c>
       <c r="M89" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1261.1774229999999</v>
       </c>
       <c r="N89" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1096.420977</v>
       </c>
       <c r="O89" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1419.731</v>
       </c>
       <c r="P89" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1489.867</v>
       </c>
       <c r="Q89" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>1450.3809999999999</v>
       </c>
       <c r="R89" s="8">
@@ -20337,27 +20506,27 @@
       <c r="J97" s="8"/>
       <c r="K97" s="8"/>
       <c r="L97" s="8">
-        <f t="shared" ref="L97:Q97" si="53">+SUM(L90:L96)</f>
+        <f t="shared" ref="L97:Q97" si="55">+SUM(L90:L96)</f>
         <v>0</v>
       </c>
       <c r="M97" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N97" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>538.11358599999994</v>
       </c>
       <c r="O97" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2410.6370000000002</v>
       </c>
       <c r="P97" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2386.6889999999999</v>
       </c>
       <c r="Q97" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2287.8610000000003</v>
       </c>
       <c r="R97" s="8">
@@ -20467,27 +20636,27 @@
       <c r="J98" s="8"/>
       <c r="K98" s="8"/>
       <c r="L98" s="8">
-        <f t="shared" ref="L98:Q98" si="54">+L97+L89</f>
+        <f t="shared" ref="L98:Q98" si="56">+L97+L89</f>
         <v>0</v>
       </c>
       <c r="M98" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>1261.1774229999999</v>
       </c>
       <c r="N98" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>1634.5345629999999</v>
       </c>
       <c r="O98" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>3830.3680000000004</v>
       </c>
       <c r="P98" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>3876.5559999999996</v>
       </c>
       <c r="Q98" s="8">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>3738.2420000000002</v>
       </c>
       <c r="R98" s="8">
@@ -20713,27 +20882,27 @@
       <c r="J100" s="8"/>
       <c r="K100" s="8"/>
       <c r="L100" s="26">
-        <f t="shared" ref="L100:Q100" si="55">+L98+L99</f>
+        <f t="shared" ref="L100:Q100" si="57">+L98+L99</f>
         <v>0</v>
       </c>
       <c r="M100" s="26">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>1261.1774229999999</v>
       </c>
       <c r="N100" s="26">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>1634.5345629999999</v>
       </c>
       <c r="O100" s="26">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>6959.0110000000004</v>
       </c>
       <c r="P100" s="26">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>7377.5779999999995</v>
       </c>
       <c r="Q100" s="26">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>7615.0510000000004</v>
       </c>
       <c r="R100" s="26">
@@ -20947,27 +21116,27 @@
       <c r="J102" s="8"/>
       <c r="K102" s="8"/>
       <c r="L102" s="8">
-        <f t="shared" ref="L102:Q102" si="56">+L35</f>
+        <f t="shared" ref="L102:Q102" si="58">+L35</f>
         <v>302.52399999999989</v>
       </c>
       <c r="M102" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>234.76</v>
       </c>
       <c r="N102" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>-51.811999999999856</v>
       </c>
       <c r="O102" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>421.65500000000037</v>
       </c>
       <c r="P102" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>710.97500000000036</v>
       </c>
       <c r="Q102" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>971.46300000000042</v>
       </c>
       <c r="R102" s="8">
@@ -22468,27 +22637,27 @@
       <c r="J115" s="8"/>
       <c r="K115" s="8"/>
       <c r="L115" s="8">
-        <f t="shared" ref="L115:Q115" si="57">+SUM(L110:L114)</f>
+        <f t="shared" ref="L115:Q115" si="59">+SUM(L110:L114)</f>
         <v>0</v>
       </c>
       <c r="M115" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="N115" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="O115" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>77.744</v>
       </c>
       <c r="P115" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>-130.07299999999998</v>
       </c>
       <c r="Q115" s="8">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>-122.90100000000001</v>
       </c>
       <c r="R115" s="8">
@@ -22830,27 +22999,27 @@
       <c r="J118" s="8"/>
       <c r="K118" s="8"/>
       <c r="L118" s="26">
-        <f t="shared" ref="L118:Q118" si="58">+SUM(L102:L109)+SUM(L115:L117)</f>
+        <f t="shared" ref="L118:Q118" si="60">+SUM(L102:L109)+SUM(L115:L117)</f>
         <v>302.52399999999989</v>
       </c>
       <c r="M118" s="26">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>234.76</v>
       </c>
       <c r="N118" s="26">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>-51.811999999999856</v>
       </c>
       <c r="O118" s="26">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>1143.5280000000002</v>
       </c>
       <c r="P118" s="26">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>1123.7070000000006</v>
       </c>
       <c r="Q118" s="26">
-        <f t="shared" si="58"/>
+        <f t="shared" si="60"/>
         <v>1155.2810000000004</v>
       </c>
       <c r="R118" s="26">
@@ -23660,27 +23829,27 @@
       <c r="J125" s="8"/>
       <c r="K125" s="8"/>
       <c r="L125" s="26">
-        <f t="shared" ref="L125:Q125" si="59">+SUM(L119:L124)</f>
+        <f t="shared" ref="L125:Q125" si="61">+SUM(L119:L124)</f>
         <v>0</v>
       </c>
       <c r="M125" s="26">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="N125" s="26">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="O125" s="26">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>-137.26499999999999</v>
       </c>
       <c r="P125" s="26">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>-250.20479999999998</v>
       </c>
       <c r="Q125" s="26">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>-759.19100000000014</v>
       </c>
       <c r="R125" s="26">
@@ -24604,27 +24773,27 @@
       <c r="J133" s="8"/>
       <c r="K133" s="8"/>
       <c r="L133" s="26">
-        <f t="shared" ref="L133:Q133" si="60">+SUM(L126:L132)</f>
+        <f t="shared" ref="L133:Q133" si="62">+SUM(L126:L132)</f>
         <v>0</v>
       </c>
       <c r="M133" s="26">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="N133" s="26">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="O133" s="26">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-494.72700000000003</v>
       </c>
       <c r="P133" s="26">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-787.37799999999993</v>
       </c>
       <c r="Q133" s="26">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-775.72799999999984</v>
       </c>
       <c r="R133" s="26">
@@ -24850,23 +25019,23 @@
       <c r="J135" s="8"/>
       <c r="K135" s="8"/>
       <c r="L135" s="8">
-        <f t="shared" ref="L135:P135" si="61">+L134+L133+L125+L118</f>
+        <f t="shared" ref="L135:P135" si="63">+L134+L133+L125+L118</f>
         <v>302.52399999999989</v>
       </c>
       <c r="M135" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>234.76</v>
       </c>
       <c r="N135" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>-51.811999999999856</v>
       </c>
       <c r="O135" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>539.39400000000023</v>
       </c>
       <c r="P135" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>109.85020000000065</v>
       </c>
       <c r="Q135" s="8">
@@ -50090,7 +50259,7 @@
       </c>
       <c r="E4" s="41">
         <f ca="1">+TODAY()</f>
-        <v>46087</v>
+        <v>46143</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>319</v>
@@ -51368,43 +51537,43 @@
       </c>
       <c r="M53" s="2">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>126.18333333333334</v>
+        <v>126.33611111111111</v>
       </c>
       <c r="N53" s="2">
         <f ca="1">M53+1</f>
-        <v>127.18333333333334</v>
+        <v>127.33611111111111</v>
       </c>
       <c r="O53" s="2">
         <f ca="1">N53+1</f>
-        <v>128.18333333333334</v>
+        <v>128.33611111111111</v>
       </c>
       <c r="P53" s="2">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>129.18333333333334</v>
+        <v>129.33611111111111</v>
       </c>
       <c r="Q53" s="2">
         <f t="shared" ca="1" si="16"/>
-        <v>130.18333333333334</v>
+        <v>130.33611111111111</v>
       </c>
       <c r="R53" s="2">
         <f t="shared" ca="1" si="16"/>
-        <v>131.18333333333334</v>
+        <v>131.33611111111111</v>
       </c>
       <c r="S53" s="2">
         <f t="shared" ca="1" si="16"/>
-        <v>132.18333333333334</v>
+        <v>132.33611111111111</v>
       </c>
       <c r="T53" s="2">
         <f t="shared" ca="1" si="16"/>
-        <v>133.18333333333334</v>
+        <v>133.33611111111111</v>
       </c>
       <c r="U53" s="2">
         <f t="shared" ca="1" si="16"/>
-        <v>134.18333333333334</v>
+        <v>134.33611111111111</v>
       </c>
       <c r="V53" s="2">
         <f t="shared" ca="1" si="16"/>
-        <v>135.18333333333334</v>
+        <v>135.33611111111111</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -51604,30 +51773,30 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B68" s="78"/>
-      <c r="C68" s="91" t="s">
+      <c r="C68" s="93" t="s">
         <v>334</v>
       </c>
-      <c r="D68" s="91"/>
-      <c r="E68" s="91"/>
-      <c r="F68" s="91"/>
-      <c r="G68" s="91"/>
-      <c r="H68" s="91"/>
-      <c r="I68" s="91"/>
-      <c r="J68" s="92"/>
+      <c r="D68" s="93"/>
+      <c r="E68" s="93"/>
+      <c r="F68" s="93"/>
+      <c r="G68" s="93"/>
+      <c r="H68" s="93"/>
+      <c r="I68" s="93"/>
+      <c r="J68" s="94"/>
       <c r="M68" s="78"/>
-      <c r="N68" s="93" t="s">
+      <c r="N68" s="95" t="s">
         <v>362</v>
       </c>
-      <c r="O68" s="93"/>
-      <c r="P68" s="93"/>
-      <c r="Q68" s="93"/>
-      <c r="R68" s="93"/>
-      <c r="S68" s="93"/>
-      <c r="T68" s="93"/>
-      <c r="U68" s="94"/>
+      <c r="O68" s="95"/>
+      <c r="P68" s="95"/>
+      <c r="Q68" s="95"/>
+      <c r="R68" s="95"/>
+      <c r="S68" s="95"/>
+      <c r="T68" s="95"/>
+      <c r="U68" s="96"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B69" s="95" t="s">
+      <c r="B69" s="97" t="s">
         <v>312</v>
       </c>
       <c r="C69" s="79" t="e">
@@ -51641,7 +51810,7 @@
       <c r="H69" s="80"/>
       <c r="I69" s="80"/>
       <c r="J69" s="80"/>
-      <c r="M69" s="95" t="s">
+      <c r="M69" s="97" t="s">
         <v>312</v>
       </c>
       <c r="N69" s="79" t="e">
@@ -51657,7 +51826,7 @@
       <c r="U69" s="80"/>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B70" s="95"/>
+      <c r="B70" s="97"/>
       <c r="C70" s="81"/>
       <c r="D70" s="82"/>
       <c r="E70" s="82"/>
@@ -51666,7 +51835,7 @@
       <c r="H70" s="82"/>
       <c r="I70" s="82"/>
       <c r="J70" s="82"/>
-      <c r="M70" s="95"/>
+      <c r="M70" s="97"/>
       <c r="N70" s="81"/>
       <c r="O70" s="82"/>
       <c r="P70" s="82"/>
@@ -51677,7 +51846,7 @@
       <c r="U70" s="82"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B71" s="95"/>
+      <c r="B71" s="97"/>
       <c r="C71" s="81"/>
       <c r="D71" s="82"/>
       <c r="E71" s="82"/>
@@ -51686,7 +51855,7 @@
       <c r="H71" s="82"/>
       <c r="I71" s="82"/>
       <c r="J71" s="82"/>
-      <c r="M71" s="95"/>
+      <c r="M71" s="97"/>
       <c r="N71" s="81"/>
       <c r="O71" s="82"/>
       <c r="P71" s="82"/>
@@ -51697,7 +51866,7 @@
       <c r="U71" s="82"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B72" s="95"/>
+      <c r="B72" s="97"/>
       <c r="C72" s="81"/>
       <c r="D72" s="83"/>
       <c r="E72" s="83"/>
@@ -51706,7 +51875,7 @@
       <c r="H72" s="83"/>
       <c r="I72" s="83"/>
       <c r="J72" s="83"/>
-      <c r="M72" s="95"/>
+      <c r="M72" s="97"/>
       <c r="N72" s="81"/>
       <c r="O72" s="83"/>
       <c r="P72" s="83"/>
@@ -51717,7 +51886,7 @@
       <c r="U72" s="83"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B73" s="95"/>
+      <c r="B73" s="97"/>
       <c r="C73" s="81"/>
       <c r="D73" s="82"/>
       <c r="E73" s="82"/>
@@ -51726,7 +51895,7 @@
       <c r="H73" s="82"/>
       <c r="I73" s="82"/>
       <c r="J73" s="82"/>
-      <c r="M73" s="95"/>
+      <c r="M73" s="97"/>
       <c r="N73" s="81"/>
       <c r="O73" s="82"/>
       <c r="P73" s="82"/>
@@ -51737,7 +51906,7 @@
       <c r="U73" s="82"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B74" s="95"/>
+      <c r="B74" s="97"/>
       <c r="C74" s="81"/>
       <c r="D74" s="82"/>
       <c r="E74" s="82"/>
@@ -51746,7 +51915,7 @@
       <c r="H74" s="82"/>
       <c r="I74" s="82"/>
       <c r="J74" s="82"/>
-      <c r="M74" s="95"/>
+      <c r="M74" s="97"/>
       <c r="N74" s="81"/>
       <c r="O74" s="82"/>
       <c r="P74" s="82"/>
@@ -51757,7 +51926,7 @@
       <c r="U74" s="82"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="95"/>
+      <c r="B75" s="97"/>
       <c r="C75" s="81"/>
       <c r="D75" s="82"/>
       <c r="E75" s="82"/>
@@ -51766,7 +51935,7 @@
       <c r="H75" s="82"/>
       <c r="I75" s="82"/>
       <c r="J75" s="82"/>
-      <c r="M75" s="95"/>
+      <c r="M75" s="97"/>
       <c r="N75" s="81"/>
       <c r="O75" s="82"/>
       <c r="P75" s="82"/>
@@ -51777,7 +51946,7 @@
       <c r="U75" s="82"/>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="96"/>
+      <c r="B76" s="98"/>
       <c r="C76" s="81"/>
       <c r="D76" s="82"/>
       <c r="E76" s="82"/>
@@ -51786,7 +51955,7 @@
       <c r="H76" s="82"/>
       <c r="I76" s="82"/>
       <c r="J76" s="82"/>
-      <c r="M76" s="96"/>
+      <c r="M76" s="98"/>
       <c r="N76" s="81"/>
       <c r="O76" s="82"/>
       <c r="P76" s="82"/>
